--- a/eval_output/品保課_詹郁瑛_評分表.xlsx
+++ b/eval_output/品保課_詹郁瑛_評分表.xlsx
@@ -1335,6 +1335,11 @@
           <t>劉祐誠</t>
         </is>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>鍾欣芳</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="36" t="inlineStr">

--- a/eval_output/品保課_詹郁瑛_評分表.xlsx
+++ b/eval_output/品保課_詹郁瑛_評分表.xlsx
@@ -1247,95 +1247,70 @@
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>白惇維</t>
+          <t>王柳琦</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>王柳琦</t>
+          <t>徐惠蘭</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>徐惠蘭</t>
+          <t>沙洋</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>沙洋</t>
+          <t>石容瑄</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>曾夷璋</t>
+          <t>陳惠萍</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>陳家祥</t>
+          <t>尤念萍</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>王秀雯</t>
+          <t>林德和</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>石容瑄</t>
+          <t>羅文彥</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>陳惠萍</t>
+          <t>楊心恬</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>尤念萍</t>
+          <t>陳巧倫</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>林德和</t>
+          <t>郭惠婷</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>羅文彥</t>
+          <t>尤秐棠</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>楊心恬</t>
+          <t>陳孟怡</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
-        <is>
-          <t>陳巧倫</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>郭惠婷</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>尤秐棠</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>陳孟怡</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>劉祐誠</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
         <is>
           <t>鍾欣芳</t>
         </is>

--- a/eval_output/品保課_詹郁瑛_評分表.xlsx
+++ b/eval_output/品保課_詹郁瑛_評分表.xlsx
@@ -224,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -341,11 +341,18 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -796,7 +803,7 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIF(D6:P6,"&lt;&gt;")</f>
+        <f>COUNTIF(D6:F6,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -1155,6 +1162,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="12">
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="A2:I2"/>
@@ -1233,7 +1241,7 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIF(D6:P6,"&lt;&gt;")</f>
+        <f>COUNTIF(D6:Q6,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -1349,6 +1357,20 @@
           <t>根據考核固定成績</t>
         </is>
       </c>
+      <c r="D8" s="38" t="n"/>
+      <c r="E8" s="38" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="38" t="n"/>
+      <c r="H8" s="38" t="n"/>
+      <c r="I8" s="38" t="n"/>
+      <c r="J8" s="38" t="n"/>
+      <c r="K8" s="38" t="n"/>
+      <c r="L8" s="38" t="n"/>
+      <c r="M8" s="38" t="n"/>
+      <c r="N8" s="38" t="n"/>
+      <c r="O8" s="38" t="n"/>
+      <c r="P8" s="38" t="n"/>
+      <c r="Q8" s="38" t="n"/>
     </row>
     <row r="9" ht="123" customHeight="1">
       <c r="A9" s="37" t="inlineStr">
@@ -1356,12 +1378,12 @@
           <t>跨部門溝通協調能力20%</t>
         </is>
       </c>
-      <c r="B9" s="38" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>跨部門協辦時，交代是否清楚？（15 分）</t>
         </is>
       </c>
-      <c r="C9" s="39" t="inlineStr">
+      <c r="C9" s="40" t="inlineStr">
         <is>
           <t>✓任務交代內容完整（目的、時程、資料、條件）；對方能一次理解；無需再次確認；無誤會或重工。 (13-15)
 ✓大部分交代清楚；偶有細節不足但不影響進度。 (10-12)
@@ -1370,7 +1392,20 @@
 ✓未交代清楚或資訊錯誤；造成流程延誤、返工或責任互推。 (0-3)</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n"/>
+      <c r="D9" s="41" t="n"/>
+      <c r="E9" s="38" t="n"/>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="38" t="n"/>
+      <c r="H9" s="38" t="n"/>
+      <c r="I9" s="38" t="n"/>
+      <c r="J9" s="38" t="n"/>
+      <c r="K9" s="38" t="n"/>
+      <c r="L9" s="38" t="n"/>
+      <c r="M9" s="38" t="n"/>
+      <c r="N9" s="38" t="n"/>
+      <c r="O9" s="38" t="n"/>
+      <c r="P9" s="38" t="n"/>
+      <c r="Q9" s="38" t="n"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="37" t="n"/>
@@ -1388,10 +1423,23 @@
 ✓反覆越權、直接指揮他人或跳主管；造成部門衝突或重大錯誤。 (0-3)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="38" t="n"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="38" t="n"/>
+      <c r="H10" s="38" t="n"/>
+      <c r="I10" s="38" t="n"/>
+      <c r="J10" s="38" t="n"/>
+      <c r="K10" s="38" t="n"/>
+      <c r="L10" s="38" t="n"/>
+      <c r="M10" s="38" t="n"/>
+      <c r="N10" s="38" t="n"/>
+      <c r="O10" s="38" t="n"/>
+      <c r="P10" s="38" t="n"/>
+      <c r="Q10" s="38" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>跨部門工作表現30%</t>
         </is>
@@ -1401,16 +1449,29 @@
           <t>*低於等於6分或高於13分，請說明原因：____________________</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="38" t="n"/>
+      <c r="F11" s="38" t="n"/>
+      <c r="G11" s="38" t="n"/>
+      <c r="H11" s="38" t="n"/>
+      <c r="I11" s="38" t="n"/>
+      <c r="J11" s="38" t="n"/>
+      <c r="K11" s="38" t="n"/>
+      <c r="L11" s="38" t="n"/>
+      <c r="M11" s="38" t="n"/>
+      <c r="N11" s="38" t="n"/>
+      <c r="O11" s="38" t="n"/>
+      <c r="P11" s="38" t="n"/>
+      <c r="Q11" s="38" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="B12" s="39" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">跨部門回覆速度與協作度（15 分）
 </t>
         </is>
       </c>
-      <c r="C12" s="41" t="inlineStr">
+      <c r="C12" s="43" t="inlineStr">
         <is>
           <t>✓回覆迅速（一般案件 30–60 分鐘內）；主動更新進度；積極協作、不推託。 (13-15)
 ✓回覆通常在當天，偶有延遲但會說明。 (10-12)
@@ -1419,26 +1480,52 @@
 ✓長期不回覆或拒絕協作；造成重大流程中斷。 (0-3)</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="38" t="n"/>
+      <c r="F12" s="38" t="n"/>
+      <c r="G12" s="38" t="n"/>
+      <c r="H12" s="38" t="n"/>
+      <c r="I12" s="38" t="n"/>
+      <c r="J12" s="38" t="n"/>
+      <c r="K12" s="38" t="n"/>
+      <c r="L12" s="38" t="n"/>
+      <c r="M12" s="38" t="n"/>
+      <c r="N12" s="38" t="n"/>
+      <c r="O12" s="38" t="n"/>
+      <c r="P12" s="38" t="n"/>
+      <c r="Q12" s="38" t="n"/>
     </row>
     <row r="13" ht="44.5" customHeight="1">
-      <c r="A13" s="42" t="n"/>
-      <c r="B13" s="43" t="inlineStr">
+      <c r="A13" s="44" t="n"/>
+      <c r="B13" s="45" t="inlineStr">
         <is>
           <t>*低於等於6分或高於13分，請說明原因：____________________</t>
         </is>
       </c>
-      <c r="C13" s="42" t="n"/>
-      <c r="D13" s="7" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="38" t="n"/>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="38" t="n"/>
+      <c r="H13" s="38" t="n"/>
+      <c r="I13" s="38" t="n"/>
+      <c r="J13" s="38" t="n"/>
+      <c r="K13" s="38" t="n"/>
+      <c r="L13" s="38" t="n"/>
+      <c r="M13" s="38" t="n"/>
+      <c r="N13" s="38" t="n"/>
+      <c r="O13" s="38" t="n"/>
+      <c r="P13" s="38" t="n"/>
+      <c r="Q13" s="38" t="n"/>
     </row>
     <row r="14" ht="70" customHeight="1">
       <c r="A14" s="37" t="n"/>
-      <c r="B14" s="44" t="inlineStr">
+      <c r="B14" s="46" t="inlineStr">
         <is>
           <t>遇到問題時，是否會先查制度流程？（15 分）</t>
         </is>
       </c>
-      <c r="C14" s="45" t="inlineStr">
+      <c r="C14" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">✓遇到問題會先查 SOP、流程、辦法，再提出問題；提問前已掌握背景資訊；80% 以上問題能自行依制度解決 (13-15)
 ✓大部分情況會查制度；偶爾先問人，但提問內容完整。 (10-12)
@@ -1448,21 +1535,47 @@
 </t>
         </is>
       </c>
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="38" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="38" t="n"/>
+      <c r="H14" s="38" t="n"/>
+      <c r="I14" s="38" t="n"/>
+      <c r="J14" s="38" t="n"/>
+      <c r="K14" s="38" t="n"/>
+      <c r="L14" s="38" t="n"/>
+      <c r="M14" s="38" t="n"/>
+      <c r="N14" s="38" t="n"/>
+      <c r="O14" s="38" t="n"/>
+      <c r="P14" s="38" t="n"/>
+      <c r="Q14" s="38" t="n"/>
     </row>
     <row r="15" ht="62.5" customHeight="1">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>跨部門工作態度
 35%</t>
         </is>
       </c>
-      <c r="B15" s="47" t="inlineStr">
+      <c r="B15" s="49" t="inlineStr">
         <is>
           <t>*低於等於6分或高於等於13分，請說明原因：_________________________</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="38" t="n"/>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="38" t="n"/>
+      <c r="H15" s="38" t="n"/>
+      <c r="I15" s="38" t="n"/>
+      <c r="J15" s="38" t="n"/>
+      <c r="K15" s="38" t="n"/>
+      <c r="L15" s="38" t="n"/>
+      <c r="M15" s="38" t="n"/>
+      <c r="N15" s="38" t="n"/>
+      <c r="O15" s="38" t="n"/>
+      <c r="P15" s="38" t="n"/>
+      <c r="Q15" s="38" t="n"/>
     </row>
     <row r="16" ht="62.5" customHeight="1">
       <c r="B16" s="25" t="inlineStr">
@@ -1479,7 +1592,20 @@
 ✓錯誤頻繁；資料重大缺漏；造成流程中斷或退件；正確率 &lt;50%。 (0-3)</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="38" t="n"/>
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="38" t="n"/>
+      <c r="H16" s="38" t="n"/>
+      <c r="I16" s="38" t="n"/>
+      <c r="J16" s="38" t="n"/>
+      <c r="K16" s="38" t="n"/>
+      <c r="L16" s="38" t="n"/>
+      <c r="M16" s="38" t="n"/>
+      <c r="N16" s="38" t="n"/>
+      <c r="O16" s="38" t="n"/>
+      <c r="P16" s="38" t="n"/>
+      <c r="Q16" s="38" t="n"/>
     </row>
     <row r="17" ht="55" customHeight="1">
       <c r="B17" s="28" t="inlineStr">
@@ -1487,7 +1613,20 @@
           <t>*低於等於8分或高於等於16分，請說明原因： _________________________</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="38" t="n"/>
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="38" t="n"/>
+      <c r="H17" s="38" t="n"/>
+      <c r="I17" s="38" t="n"/>
+      <c r="J17" s="38" t="n"/>
+      <c r="K17" s="38" t="n"/>
+      <c r="L17" s="38" t="n"/>
+      <c r="M17" s="38" t="n"/>
+      <c r="N17" s="38" t="n"/>
+      <c r="O17" s="38" t="n"/>
+      <c r="P17" s="38" t="n"/>
+      <c r="Q17" s="38" t="n"/>
     </row>
     <row r="18" ht="23.5" customHeight="1">
       <c r="C18" s="32" t="inlineStr">
@@ -1495,11 +1634,63 @@
           <t>總分</t>
         </is>
       </c>
-      <c r="D18" s="48">
+      <c r="D18" s="50">
         <f>SUM(D8:D17)</f>
         <v/>
       </c>
-      <c r="AK18" s="49" t="n"/>
+      <c r="E18" s="50">
+        <f>SUM(E8:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="50">
+        <f>SUM(F8:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="50">
+        <f>SUM(G8:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="50">
+        <f>SUM(H8:H17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="50">
+        <f>SUM(I8:I17)</f>
+        <v/>
+      </c>
+      <c r="J18" s="50">
+        <f>SUM(J8:J17)</f>
+        <v/>
+      </c>
+      <c r="K18" s="50">
+        <f>SUM(K8:K17)</f>
+        <v/>
+      </c>
+      <c r="L18" s="50">
+        <f>SUM(L8:L17)</f>
+        <v/>
+      </c>
+      <c r="M18" s="50">
+        <f>SUM(M8:M17)</f>
+        <v/>
+      </c>
+      <c r="N18" s="50">
+        <f>SUM(N8:N17)</f>
+        <v/>
+      </c>
+      <c r="O18" s="50">
+        <f>SUM(O8:O17)</f>
+        <v/>
+      </c>
+      <c r="P18" s="50">
+        <f>SUM(P8:P17)</f>
+        <v/>
+      </c>
+      <c r="Q18" s="50">
+        <f>SUM(Q8:Q17)</f>
+        <v/>
+      </c>
+      <c r="AK18" s="51" t="n"/>
     </row>
     <row r="19">
       <c r="D19" s="7">
@@ -1512,8 +1703,139 @@
 ), "⚠ 超標！", "")</f>
         <v/>
       </c>
+      <c r="E19" s="7">
+        <f>IF(OR(
+  AND(E18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(E18&gt;=80,E18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(E18&gt;=70,E18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(E18&gt;=60,E18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(E18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="F19" s="7">
+        <f>IF(OR(
+  AND(F18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(F18&gt;=80,F18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(F18&gt;=70,F18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(F18&gt;=60,F18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(F18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="G19" s="7">
+        <f>IF(OR(
+  AND(G18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(G18&gt;=80,G18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(G18&gt;=70,G18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(G18&gt;=60,G18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(G18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="H19" s="7">
+        <f>IF(OR(
+  AND(H18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(H18&gt;=80,H18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(H18&gt;=70,H18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(H18&gt;=60,H18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(H18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="I19" s="7">
+        <f>IF(OR(
+  AND(I18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(I18&gt;=80,I18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(I18&gt;=70,I18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(I18&gt;=60,I18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(I18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="J19" s="7">
+        <f>IF(OR(
+  AND(J18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(J18&gt;=80,J18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(J18&gt;=70,J18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(J18&gt;=60,J18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(J18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="K19" s="7">
+        <f>IF(OR(
+  AND(K18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(K18&gt;=80,K18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(K18&gt;=70,K18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(K18&gt;=60,K18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(K18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="L19" s="7">
+        <f>IF(OR(
+  AND(L18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(L18&gt;=80,L18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(L18&gt;=70,L18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(L18&gt;=60,L18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(L18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="M19" s="7">
+        <f>IF(OR(
+  AND(M18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(M18&gt;=80,M18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(M18&gt;=70,M18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(M18&gt;=60,M18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(M18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="N19" s="7">
+        <f>IF(OR(
+  AND(N18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(N18&gt;=80,N18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(N18&gt;=70,N18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(N18&gt;=60,N18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(N18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="O19" s="7">
+        <f>IF(OR(
+  AND(O18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(O18&gt;=80,O18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(O18&gt;=70,O18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(O18&gt;=60,O18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(O18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="P19" s="7">
+        <f>IF(OR(
+  AND(P18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(P18&gt;=80,P18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(P18&gt;=70,P18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(P18&gt;=60,P18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(P18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="Q19" s="7">
+        <f>IF(OR(
+  AND(Q18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
+  AND(Q18&gt;=80,Q18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
+  AND(Q18&gt;=70,Q18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
+  AND(Q18&gt;=60,Q18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
+  AND(Q18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="9">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C12:C13"/>
